--- a/Class files/Nested-if_&_count-sum_variants - Format.xlsx
+++ b/Class files/Nested-if_&_count-sum_variants - Format.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Excel files\Class files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99D2C821-2D11-48B9-AE2E-6E99F91A5B69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91C48296-C0DA-4739-9AFA-3F8136CC2CAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1145,21 +1145,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1167,7 +1167,7 @@
   </cellStyles>
   <dxfs count="21">
     <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -1176,7 +1176,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <fill>
@@ -1472,11 +1472,11 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AE0515B8-A168-4761-BE65-AEFF02408EDF}" name="Avg_Sales" displayName="Avg_Sales" ref="N25:O30" totalsRowShown="0" headerRowDxfId="0" dataDxfId="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AE0515B8-A168-4761-BE65-AEFF02408EDF}" name="Avg_Sales" displayName="Avg_Sales" ref="N25:O30" totalsRowShown="0" headerRowDxfId="3" dataDxfId="2">
   <autoFilter ref="N25:O30" xr:uid="{AE0515B8-A168-4761-BE65-AEFF02408EDF}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{4DCB57D1-E119-4154-AA62-6D44B389FE7F}" name="Region " dataDxfId="3"/>
-    <tableColumn id="2" xr3:uid="{CF18188A-B750-493E-95AC-382868DE431B}" name="Avg_Sales" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{4DCB57D1-E119-4154-AA62-6D44B389FE7F}" name="Region " dataDxfId="1"/>
+    <tableColumn id="2" xr3:uid="{CF18188A-B750-493E-95AC-382868DE431B}" name="Avg_Sales" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1677,13 +1677,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="51" t="s">
+      <c r="A1" s="55" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="51"/>
-      <c r="C1" s="51"/>
-      <c r="D1" s="51"/>
-      <c r="E1" s="51"/>
+      <c r="B1" s="55"/>
+      <c r="C1" s="55"/>
+      <c r="D1" s="55"/>
+      <c r="E1" s="55"/>
     </row>
     <row r="2" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -2286,13 +2286,13 @@
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
-      <c r="R1" s="51" t="s">
+      <c r="R1" s="55" t="s">
         <v>50</v>
       </c>
-      <c r="S1" s="51"/>
-      <c r="T1" s="51"/>
-      <c r="U1" s="51"/>
-      <c r="V1" s="51"/>
+      <c r="S1" s="55"/>
+      <c r="T1" s="55"/>
+      <c r="U1" s="55"/>
+      <c r="V1" s="55"/>
     </row>
     <row r="2" spans="1:32" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="14" t="s">
@@ -2341,13 +2341,13 @@
       <c r="N2" s="50"/>
       <c r="O2" s="50"/>
       <c r="P2" s="50"/>
-      <c r="R2" s="52" t="s">
+      <c r="R2" s="56" t="s">
         <v>51</v>
       </c>
-      <c r="S2" s="52"/>
-      <c r="T2" s="52"/>
-      <c r="U2" s="52"/>
-      <c r="V2" s="52"/>
+      <c r="S2" s="56"/>
+      <c r="T2" s="56"/>
+      <c r="U2" s="56"/>
+      <c r="V2" s="56"/>
     </row>
     <row r="3" spans="1:32" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="18" t="s">
@@ -3837,10 +3837,10 @@
         <v>High</v>
       </c>
       <c r="M25" s="50"/>
-      <c r="N25" s="56" t="s">
+      <c r="N25" s="54" t="s">
         <v>167</v>
       </c>
-      <c r="O25" s="56" t="s">
+      <c r="O25" s="54" t="s">
         <v>166</v>
       </c>
       <c r="P25" s="50"/>
@@ -4172,13 +4172,13 @@
         <v>52689.25</v>
       </c>
       <c r="P30" s="50"/>
-      <c r="S30" s="55" t="s">
+      <c r="S30" s="53" t="s">
         <v>170</v>
       </c>
-      <c r="T30" s="54" t="s">
+      <c r="T30" s="52" t="s">
         <v>171</v>
       </c>
-      <c r="U30" s="53">
+      <c r="U30" s="51">
         <f>AVERAGEIFS(D2:D31,B2:B31,"=West",E2:E31,"=Completed")</f>
         <v>64593.833333333336</v>
       </c>
@@ -4230,31 +4230,31 @@
       <c r="N31" s="50"/>
       <c r="O31" s="50"/>
       <c r="P31" s="50"/>
-      <c r="S31" s="55" t="s">
+      <c r="S31" s="53" t="s">
         <v>165</v>
       </c>
-      <c r="T31" s="54" t="s">
+      <c r="T31" s="52" t="s">
         <v>163</v>
       </c>
-      <c r="U31" s="54">
+      <c r="U31" s="52">
         <f>COUNTIFS(L2:L31,"=High",E2:E31,"=Completed")</f>
         <v>7</v>
       </c>
     </row>
     <row r="32" spans="1:22" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="S32" s="55" t="s">
+      <c r="S32" s="53" t="s">
         <v>165</v>
       </c>
-      <c r="T32" s="54" t="s">
+      <c r="T32" s="52" t="s">
         <v>164</v>
       </c>
-      <c r="U32" s="54">
+      <c r="U32" s="52">
         <f>COUNTIFS(D2:D31,"&gt;=60000",E2:E31,"=Completed")</f>
         <v>7</v>
       </c>
     </row>
     <row r="33" spans="20:20" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="T33" s="54"/>
+      <c r="T33" s="52"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:L31" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
@@ -4285,12 +4285,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="51" t="s">
+      <c r="A1" s="55" t="s">
         <v>118</v>
       </c>
-      <c r="B1" s="51"/>
-      <c r="C1" s="51"/>
-      <c r="D1" s="51"/>
+      <c r="B1" s="55"/>
+      <c r="C1" s="55"/>
+      <c r="D1" s="55"/>
     </row>
     <row r="2" spans="1:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
